--- a/output/原町赤十字病院_随意契約_X線関連.xlsx
+++ b/output/原町赤十字病院_随意契約_X線関連.xlsx
@@ -671,7 +671,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>不明（R5.4.1〜R5.4.1）</t>
+          <t>不明（令和5年4月1日〜R5.4.1）</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
